--- a/dtw-it-center-pm-toolkit/02-technology-project/02_PM_Tracking_Workbook.xlsx
+++ b/dtw-it-center-pm-toolkit/02-technology-project/02_PM_Tracking_Workbook.xlsx
@@ -11,11 +11,12 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="WBS_Schedule" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Budget_Tracker" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="RACI_Matrix" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Stakeholder_Register" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Risk_Register" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Issue_Change_Log" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Vendor_Contractor_Register" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Quality_Checklist" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="RACI_Matrix" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Stakeholder_Register" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Risk_Register" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Issue_Change_Log" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Vendor_Contractor_Register" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="236">
   <si>
     <t xml:space="preserve">IT Center Network &amp; Airport Operations Systems Modernization — PM Tracking Workbook</t>
   </si>
@@ -311,6 +312,81 @@
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
+    <t xml:space="preserve">Quality Control Checklist  (deliverable/checkpoint acceptance tracking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptance Criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspection Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiber backbone install &amp; test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backbone validated at full design capacity with redundant failover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Integrator test + Network Eng witness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core network cutover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All concourses live on new core with zero unplanned downtime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-cutover monitoring review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations system migration (passenger/baggage/access-control)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full backup taken; system passes functional acceptance test before legacy decommission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Integrator acceptance test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month 6-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segmentation, MFA, and patch compliance verified against technical standards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity Lead sign-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go-live / hypercare exit review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support ticket volume returns to steady-state within 30 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk metrics review</t>
+  </si>
+  <si>
     <t xml:space="preserve">RACI Matrix  (R = Responsible · A = Accountable · C = Consulted · I = Informed)</t>
   </si>
   <si>
@@ -347,9 +423,6 @@
     <t xml:space="preserve">Backbone install &amp; test</t>
   </si>
   <si>
-    <t xml:space="preserve">Core network cutover</t>
-  </si>
-  <si>
     <t xml:space="preserve">Operations systems migration</t>
   </si>
   <si>
@@ -468,9 +541,6 @@
   </si>
   <si>
     <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
   </si>
   <si>
     <t xml:space="preserve">Probability (1-5)</t>
@@ -1980,11 +2050,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1997,245 +2072,148 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>101</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2252,6 +2230,278 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2264,7 +2514,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2274,42 +2524,42 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2317,19 +2567,19 @@
         <v>23</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2337,99 +2587,99 @@
         <v>63</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2446,7 +2696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2467,7 +2717,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2480,25 +2730,25 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>13</v>
@@ -2509,13 +2759,13 @@
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="D3" s="10" t="n">
         <v>2</v>
@@ -2528,21 +2778,21 @@
         <v>10</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>31</v>
@@ -2558,24 +2808,24 @@
         <v>8</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>3</v>
@@ -2588,24 +2838,24 @@
         <v>6</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>3</v>
@@ -2618,24 +2868,24 @@
         <v>9</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>63</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>3</v>
@@ -2648,24 +2898,24 @@
         <v>9</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>2</v>
@@ -2678,13 +2928,13 @@
         <v>10</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>38</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2701,7 +2951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2721,7 +2971,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2733,39 +2983,39 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>18</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>50</v>
@@ -2774,24 +3024,24 @@
         <v>30</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>50</v>
@@ -2800,13 +3050,13 @@
         <v>63</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2823,7 +3073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2841,7 +3091,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2852,13 +3102,13 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>14</v>
@@ -2867,18 +3117,18 @@
         <v>15</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>980000</v>
@@ -2890,18 +3140,18 @@
         <v>46</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C4" s="14" t="n">
         <v>850000</v>
@@ -2913,18 +3163,18 @@
         <v>64</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>268000</v>
@@ -2936,18 +3186,18 @@
         <v>64</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>300000</v>
@@ -2959,10 +3209,10 @@
         <v>40</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
